--- a/week-1/Ex4C_GTrends_marketing.xlsx
+++ b/week-1/Ex4C_GTrends_marketing.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="164" documentId="8_{20DBB84E-AD0A-47F3-9E0F-52142984FDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0849D5C8-829B-4939-B757-5789A036E85B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{6C96D55D-D4A2-4A61-8142-BC3EA8BB4F45}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="2" xr2:uid="{6C96D55D-D4A2-4A61-8142-BC3EA8BB4F45}"/>
   </bookViews>
   <sheets>
     <sheet name="by search term" sheetId="1" r:id="rId1"/>
